--- a/DownloadedExcels/ProductExclusionFile.xlsx
+++ b/DownloadedExcels/ProductExclusionFile.xlsx
@@ -65,7 +65,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -95,6 +95,33 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PL000000035</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DIST</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>15437620</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>C14835</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>62732109</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
